--- a/data/vendor-search/results_all_home-power.xlsx
+++ b/data/vendor-search/results_all_home-power.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +492,11 @@
           <t>cpe:2.3:a:enphase:envoy:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>enphase envoy</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
           <t>cpe:2.3:a:enphase:envoy:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>enphase envoy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +572,11 @@
           <t>cpe:2.3:a:enphase:envoy:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>enphase envoy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,6 +612,11 @@
           <t>cpe:2.3:o:fronius:datamanager_box_2.0_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:datamanager_box_2.0:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:eco_25.0-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:eco_25.0-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:eco_27.0-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:eco_27.0-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_1.5-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_1.5-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_1.5-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_1.5-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_2.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_2.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_2.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_2.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_2.5-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_2.5-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_2.5-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_2.5-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_3.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_3.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_3.1-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_3.1-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_3.1-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_3.1-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_10.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_10.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_11.4-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_11.4-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_12.5-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_12.5-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_15.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_15.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_3.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_3.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_3.5-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_3.5-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_3.6-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_3.6-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_3.8-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_3.8-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_4.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_4.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_4.6-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_4.6-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_5.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_5.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_5.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_5.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_5.0-1_aus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_5.0-1_aus:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_5.0-1_sc_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_5.0-1_sc:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_6.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_6.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_6.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_6.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_7.6-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_7.6-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_8.2-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_8.2-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_8.2-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_8.2-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_10.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_10.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_10.0-3-m-os_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_10.0-3-m-os:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_10.0-3_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_10.0-3_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_10.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_10.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_12.0-3_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_12.0-3_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_12.5-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_12.5-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_12.5-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_12.5-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_15.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_15.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_15.0-3_107_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_15.0-3_107:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_15.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_15.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_17.5-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_17.5-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_17.5-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_17.5-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_20.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_20.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_20.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_20.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_22.7-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_22.7-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_24.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_24.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_3.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_3.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_3.0-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_3.0-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_3.7-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_3.7-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_3.7-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_3.7-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_4.5-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_4.5-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_4.5-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_4.5-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_5.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_5.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_6.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_6.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_7.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_7.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_8.2-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_8.2-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_10.0-3_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_10.0-3_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_12.0-3_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_12.0-3_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_15.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_15.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_20.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_20.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_22.7-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_22.7-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_24.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_24.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_hybrid_3.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_hybrid_3.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_hybrid_4.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_hybrid_4.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_hybrid_5.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_hybrid_5.0-3-m:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>fronius solar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -627,6 +652,11 @@
           <t>cpe:2.3:o:fronius:datamanager_box_2.0_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:datamanager_box_2.0:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:eco_25.0-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:eco_25.0-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:eco_27.0-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:eco_27.0-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_1.5-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_1.5-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_1.5-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_1.5-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_2.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_2.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_2.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_2.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_2.5-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_2.5-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_2.5-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_2.5-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_3.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_3.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_3.1-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_3.1-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:galvo_3.1-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:galvo_3.1-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_10.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_10.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_11.4-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_11.4-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_12.5-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_12.5-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_15.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_15.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_3.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_3.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_3.5-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_3.5-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_3.6-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_3.6-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_3.8-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_3.8-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_4.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_4.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_4.6-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_4.6-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_5.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_5.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_5.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_5.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_5.0-1_aus_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_5.0-1_aus:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_5.0-1_sc_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_5.0-1_sc:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_6.0-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_6.0-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_6.0-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_6.0-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_7.6-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_7.6-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_8.2-1_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_8.2-1:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:primo_8.2-1_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:primo_8.2-1_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_10.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_10.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_10.0-3-m-os_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_10.0-3-m-os:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_10.0-3_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_10.0-3_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_10.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_10.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_12.0-3_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_12.0-3_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_12.5-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_12.5-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_12.5-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_12.5-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_15.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_15.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_15.0-3_107_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_15.0-3_107:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_15.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_15.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_17.5-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_17.5-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_17.5-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_17.5-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_20.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_20.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_20.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_20.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_22.7-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_22.7-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_24.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_24.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_3.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_3.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_3.0-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_3.0-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_3.7-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_3.7-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_3.7-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_3.7-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_4.5-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_4.5-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_4.5-3-s_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_4.5-3-s:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_5.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_5.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_6.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_6.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_7.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_7.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_8.2-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_8.2-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_10.0-3_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_10.0-3_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_12.0-3_208-240_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_12.0-3_208-240:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_15.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_15.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_20.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_20.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_22.7-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_22.7-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_advanced_24.0-3_480_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_advanced_24.0-3_480:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_hybrid_3.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_hybrid_3.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_hybrid_4.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_hybrid_4.0-3-m:-:*:*:*:*:*:*:*|cpe:2.3:o:fronius:symo_hybrid_5.0-3-m_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:fronius:symo_hybrid_5.0-3-m:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>fronius solar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -658,6 +688,11 @@
           <t>cpe:2.3:a:sma:sunny_explorer:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -693,6 +728,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -728,6 +768,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -763,6 +808,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -798,6 +848,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -833,6 +888,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -868,6 +928,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -903,6 +968,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -938,6 +1008,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -973,6 +1048,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1008,6 +1088,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1043,6 +1128,11 @@
           <t>cpe:2.3:a:sma:sunny_explorer:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1078,6 +1168,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*|cpe:2.3:a:sma:sunny_explorer:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1109,6 +1204,11 @@
           <t>cpe:2.3:o:sma:sunny_boy_3600_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_core1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_core1:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_15000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_15000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_20000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_20000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_25000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_25000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_12000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_12000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_tripower_60_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_tripower_60:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3600tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3600tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5000tl_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5000tl:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_1.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_1.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_2.5:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_3.6_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_3.6:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_4.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_4.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_5.0_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_5.0:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_1000cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_1000cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_800cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_800cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_850cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_850cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_900cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_900cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_500cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_500cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_630cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_630cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_720cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_720cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_760cp_xt_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_760cp_xt:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_500_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_500:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_630_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_630:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_720_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_720:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_760_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_760:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_800_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_800:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_850_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_850:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_900_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_900:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_1000_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_1000:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2200_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2200:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_central_storage_2500-ev_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_central_storage_2500-ev:-:*:*:*:*:*:*:*|cpe:2.3:o:sma:sunny_boy_storage_2.5_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:sma:sunny_boy_storage_2.5:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1140,6 +1240,11 @@
           <t>cpe:2.3:o:victronenergy:venus_os:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>victron energy</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1175,6 +1280,11 @@
           <t>cpe:2.3:o:enphase:envoy_firmware:d4.0:*:*:*:*:*:*:*|cpe:2.3:o:enphase:envoy_firmware:r3.0:*:*:*:*:*:*:*|cpe:2.3:h:enphase:envoy:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>enphase envoy</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1206,6 +1316,11 @@
           <t>cpe:2.3:o:enphase:envoy_firmware:d4.0:*:*:*:*:*:*:*|cpe:2.3:o:enphase:envoy_firmware:r3.0:*:*:*:*:*:*:*|cpe:2.3:h:enphase:envoy:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>enphase envoy</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1241,6 +1356,11 @@
           <t>cpe:2.3:o:enphase:envoy_firmware:d4.0:*:*:*:*:*:*:*|cpe:2.3:o:enphase:envoy_firmware:r3.0:*:*:*:*:*:*:*|cpe:2.3:h:enphase:envoy:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>enphase envoy</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1274,6 +1394,11 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>cpe:2.3:o:enphase:envoy_firmware:d4.0:*:*:*:*:*:*:*|cpe:2.3:o:enphase:envoy_firmware:r3.0:*:*:*:*:*:*:*|cpe:2.3:h:enphase:envoy:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>enphase envoy</t>
         </is>
       </c>
     </row>
@@ -1313,6 +1438,11 @@
           <t>cpe:2.3:o:enphase:envoy_firmware:d7.0.88:*:*:*:*:*:*:*|cpe:2.3:h:enphase:envoy:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>enphase envoy</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1348,6 +1478,11 @@
           <t>cpe:2.3:o:enphase:iq_gateway_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:enphase:iq_gateway:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>enphase iq</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1383,6 +1518,11 @@
           <t>cpe:2.3:o:enphase:iq_gateway_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:enphase:iq_gateway:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>enphase iq</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1418,6 +1558,11 @@
           <t>cpe:2.3:o:enphase:iq_gateway_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:enphase:iq_gateway:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>enphase iq</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1453,6 +1598,11 @@
           <t>cpe:2.3:o:enphase:iq_gateway_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:enphase:iq_gateway:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>enphase iq</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1488,6 +1638,11 @@
           <t>cpe:2.3:o:enphase:iq_gateway_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:enphase:iq_gateway:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>enphase iq</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1519,6 +1674,11 @@
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>sunny boy</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1554,6 +1714,11 @@
           <t>cpe:2.3:a:solaredge:solaredge_monitoring_platform:-:*:*:*:*:saas:*:*</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>solaredge monitoring</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1585,6 +1750,11 @@
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>solax power</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
